--- a/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
+++ b/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$A$1:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$1:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1231,11 +1231,71 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Financial Info &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Norm Ai</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Khosla Ventures</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>AI-native regulatory-compliance and legal-review platform deploying rules-trained agents for banks, insurers, asset managers and other regulated enterprises</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M3"/>
+  <autoFilter ref="A1:M4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
+++ b/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Growth Capital Raises" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$A$1:$R$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$A$1:$R$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1009,14 +1009,103 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Strategic M&amp;A</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>08-Jul-26</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Cypher</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Nium</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Crypto-native non-custodial wallet and card-issuing platform bridging fiat and on-chain money movement</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R6"/>
+  <autoFilter ref="A1:R7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
+++ b/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Growth Capital Raises" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$A$1:$R$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$B$3:$R$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$3:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0&quot;x&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\);&quot;$&quot;\ \–?"/>
+    <numFmt numFmtId="166" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,17 +34,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="8"/>
     </font>
     <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <color rgb="000563C1"/>
-      <sz val="11"/>
+      <sz val="8"/>
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,11 +59,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6FB2"/>
+        <fgColor rgb="FF0069A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0067A5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -64,36 +77,47 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00D9D9D9"/>
       </top>
+    </border>
+    <border>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,380 +484,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A3:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="2.73" customWidth="1" min="1" max="1"/>
+    <col width="12.54" customWidth="1" min="2" max="2"/>
+    <col width="14.73" customWidth="1" min="3" max="3"/>
+    <col width="14.73" customWidth="1" min="4" max="4"/>
+    <col width="15.18" customWidth="1" min="5" max="5"/>
+    <col width="11.73" customWidth="1" min="6" max="6"/>
+    <col width="17.73" customWidth="1" min="7" max="7"/>
+    <col width="20.73" customWidth="1" min="8" max="8"/>
+    <col width="12.73" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="106.73" customWidth="1" min="12" max="12"/>
+    <col width="12.73" customWidth="1" min="13" max="13"/>
+    <col width="12.73" customWidth="1" min="14" max="14"/>
+    <col width="10.73" customWidth="1" min="15" max="15"/>
+    <col width="15.73" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Target Country</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Deal Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Acquirer</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>EV ($M)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>EV / Revenue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Target Description</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Link / Press Release</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Mults Source</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>Mults Basis</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>Public Deal</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>HL Deal</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>Seller</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10-Jul-26</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Asset &amp; Wealth Tech</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Strategic M&amp;A</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>09-Jul-26</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>WIZE</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Banyan Software</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>All-in-one wealth- and asset-management platform — portfolio management, CRM, compliance and order management — for external asset managers and private banks; Banyan took a majority (control) stake, founders retaining minority</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10-Jul-26</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Financial Function</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Strategic M&amp;A</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>07-Jul-26</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Arc Technologies</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Axos Financial</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>AI-native corporate finance platform for business cash management, debt-financing access and financial-workflow automation</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>10-Jul-26</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Financial Function</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Asset &amp; Wealth Tech</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>07-Jul-26</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Notch Financial</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Telpay</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Accounts-receivable automation software for invoicing, payment collection and order management</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>09-Jul-26</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>WIZE</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Banyan Software</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>All-in-one wealth- and asset-management platform — portfolio management, CRM, compliance and order management — for external asset managers and private banks; Banyan took a majority (control) stake, founders retaining minority</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -841,81 +689,87 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>10-Jul-26</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Financial Info &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Corporate Financial Function</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>07-Jul-26</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Círculo de Crédito</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Consumer credit bureau in Mexico providing credit reports, scores and risk analytics to lenders</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Arc Technologies</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Axos Financial</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>AI-native corporate finance platform for business cash management, debt-financing access and financial-workflow automation</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Equifax investor press release</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>LTM to 30-Jun-26 rev ~$134M (+31% YoY), adj. EBITDA ~$62M; EV $750M ($825M gross less ~$75M cash, no debt) -&gt; 5.6x rev / 12.1x EBITDA</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -923,87 +777,87 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>10-Jul-26</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>InsurTech</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Corporate Financial Function</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>07-Jul-26</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Send Technology Solutions</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Duck Creek Technologies</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>AI-native underwriting orchestration engine for commercial, specialty, reinsurance and MGA/delegated-authority insurers</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Notch Financial</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Telpay</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Accounts-receivable automation software for invoicing, payment collection and order management</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1011,101 +865,271 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>10-Jul-26</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Financial Info &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Strategic M&amp;A</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Círculo de Crédito</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Consumer credit bureau in Mexico providing credit reports, scores and risk analytics to lenders</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>Equifax investor press release</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>LTM to 30-Jun-26 rev ~$134M (+31% YoY), adj. EBITDA ~$62M; EV $750M ($825M gross less ~$75M cash, no debt) -&gt; 5.6x rev / 12.1x EBITDA</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>InsurTech</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Strategic M&amp;A</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Send Technology Solutions</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Duck Creek Technologies</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>AI-native underwriting orchestration engine for commercial, specialty, reinsurance and MGA/delegated-authority insurers</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>08-Jul-26</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Cypher</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Nium</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Crypto-native non-custodial wallet and card-issuing platform bridging fiat and on-chain money movement</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R7"/>
+  <autoFilter ref="B3:R9"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1117,274 +1141,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A3:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="2.73" customWidth="1" min="1" max="1"/>
+    <col width="12.54" customWidth="1" min="2" max="2"/>
+    <col width="14.73" customWidth="1" min="3" max="3"/>
+    <col width="15.27" customWidth="1" min="4" max="4"/>
+    <col width="11.73" customWidth="1" min="5" max="5"/>
+    <col width="17.73" customWidth="1" min="6" max="6"/>
+    <col width="26.73" customWidth="1" min="7" max="7"/>
+    <col width="12.73" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="102.73" customWidth="1" min="12" max="12"/>
+    <col width="12.73" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Target Country</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Lead Investor(s)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Amount ($M)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Valuation ($M)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>EV / Revenue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Target Description</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Link / Press Release</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10-Jul-26</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Banking &amp; Lending Tech</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>07-Jul-26</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Super.com</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>TPG</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Consumer 'savings super-app' bundling cashback, credit-building and savings tools, built on a travel-and-commerce booking marketplace</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10-Jul-26</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Capital Markets Tech</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>07-Jul-26</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>EDX Markets</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>SBI Holdings</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Institutional-only digital-asset trading venue paired with a separate central clearinghouse to reduce counterparty risk</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Link</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>10-Jul-26</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Banking &amp; Lending Tech</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Super.com</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>TPG</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Consumer 'savings super-app' bundling cashback, credit-building and savings tools, built on a travel-and-commerce booking marketplace</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Capital Markets Tech</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>EDX Markets</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>SBI Holdings</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Institutional-only digital-asset trading venue paired with a separate central clearinghouse to reduce counterparty risk</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Financial Info &amp; Analytics</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>07-Jul-26</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Norm Ai</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Khosla Ventures</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H6" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I6" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>AI-native regulatory-compliance and legal-review platform deploying rules-trained agents for banks, insurers, asset managers and other regulated enterprises</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M4"/>
+  <autoFilter ref="A3:M6"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
+++ b/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Growth Capital Raises" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$B$3:$R$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$B$3:$R$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$3:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:R9"/>
+  <dimension ref="A3:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.73" customWidth="1" min="1" max="1"/>
@@ -872,46 +872,52 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Financial Info &amp; Analytics</t>
+          <t>Corporate Financial Function</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Strategic M&amp;A</t>
+          <t>PE Buyout</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>07-Jul-26</t>
+          <t>08-Jul-26</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Círculo de Crédito</t>
+          <t>ThrivePass</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>12.1</v>
+          <t>Shore Capital Partners</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Consumer credit bureau in Mexico providing credit reports, scores and risk analytics to lenders</t>
+          <t>Employee-benefits administration platform for lifestyle spending accounts, pre-tax benefits, COBRA and tuition reimbursement — HR-benefits tech with an embedded spending-account/money-movement layer</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -921,12 +927,12 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>Equifax investor press release</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>LTM to 30-Jun-26 rev ~$134M (+31% YoY), adj. EBITDA ~$62M; EV $750M ($825M gross less ~$75M cash, no debt) -&gt; 5.6x rev / 12.1x EBITDA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -954,12 +960,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>InsurTech</t>
+          <t>Financial Info &amp; Analytics</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -974,32 +980,26 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Send Technology Solutions</t>
+          <t>Círculo de Crédito</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Duck Creek Technologies</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>12.1</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>AI-native underwriting orchestration engine for commercial, specialty, reinsurance and MGA/delegated-authority insurers</t>
+          <t>Consumer credit bureau in Mexico providing credit reports, scores and risk analytics to lenders</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Equifax investor press release</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>LTM to 30-Jun-26 rev ~$134M (+31% YoY), adj. EBITDA ~$62M; EV $750M ($825M gross less ~$75M cash, no debt) -&gt; 5.6x rev / 12.1x EBITDA</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -1042,87 +1042,175 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>InsurTech</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Strategic M&amp;A</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Send Technology Solutions</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Duck Creek Technologies</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>AI-native underwriting orchestration engine for commercial, specialty, reinsurance and MGA/delegated-authority insurers</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>08-Jul-26</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Cypher</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Nium</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>Crypto-native non-custodial wallet and card-issuing platform bridging fiat and on-chain money movement</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R9"/>
+  <autoFilter ref="B3:R10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
@@ -1130,6 +1218,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
+++ b/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$B$3:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$3:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$3:$M$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:M6"/>
+  <dimension ref="A3:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.73" customWidth="1" min="1" max="1"/>
@@ -1492,12 +1492,74 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Real Estate &amp; Mortgage Tech</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>08-Jul-26</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Kord</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Guinness Ventures</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>FCA-regulated platform unifying identity/AML checks and client-money payment processing for estate agents, conveyancers and law firms</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:M6"/>
+  <autoFilter ref="A3:M7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
+++ b/weekly-deals/outputs/Weekly_Fintech_Deals_2026-07-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Growth Capital Raises" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$B$3:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$3:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All M&amp;A (PE &amp; Strategic)'!$B$3:$R$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Growth Capital Raises'!$A$3:$M$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:R10"/>
+  <dimension ref="A3:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.73" customWidth="1" min="1" max="1"/>
@@ -960,46 +960,52 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Financial Info &amp; Analytics</t>
+          <t>Corporate Financial Function</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Strategic M&amp;A</t>
+          <t>PE Buyout</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>07-Jul-26</t>
+          <t>09-Jul-26</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Círculo de Crédito</t>
+          <t>BrightAnalytics</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>12.1</v>
+          <t>PSG Equity</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Consumer credit bureau in Mexico providing credit reports, scores and risk analytics to lenders</t>
+          <t>AI-powered corporate performance management (CPM) software for CFOs — financial consolidation, reporting and FP&amp;A</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
@@ -1009,12 +1015,12 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Equifax investor press release</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>LTM to 30-Jun-26 rev ~$134M (+31% YoY), adj. EBITDA ~$62M; EV $750M ($825M gross less ~$75M cash, no debt) -&gt; 5.6x rev / 12.1x EBITDA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -1042,12 +1048,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>InsurTech</t>
+          <t>Financial Info &amp; Analytics</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1062,32 +1068,26 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Send Technology Solutions</t>
+          <t>Círculo de Crédito</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Duck Creek Technologies</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>12.1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>AI-native underwriting orchestration engine for commercial, specialty, reinsurance and MGA/delegated-authority insurers</t>
+          <t>Consumer credit bureau in Mexico providing credit reports, scores and risk analytics to lenders</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Equifax investor press release</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>LTM to 30-Jun-26 rev ~$134M (+31% YoY), adj. EBITDA ~$62M; EV $750M ($825M gross less ~$75M cash, no debt) -&gt; 5.6x rev / 12.1x EBITDA</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
@@ -1130,87 +1130,175 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>InsurTech</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Strategic M&amp;A</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Send Technology Solutions</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Duck Creek Technologies</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>AI-native underwriting orchestration engine for commercial, specialty, reinsurance and MGA/delegated-authority insurers</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Strategic M&amp;A</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>08-Jul-26</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Cypher</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Nium</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Crypto-native non-custodial wallet and card-issuing platform bridging fiat and on-chain money movement</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R10"/>
+  <autoFilter ref="B3:R11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
@@ -1219,6 +1307,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1230,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:M7"/>
+  <dimension ref="A3:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.73" customWidth="1" min="1" max="1"/>
@@ -1381,7 +1470,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Capital Markets Tech</t>
+          <t>Banking &amp; Lending Tech</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1391,21 +1480,21 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>07-Jul-26</t>
+          <t>09-Jul-26</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>EDX Markets</t>
+          <t>MountainSeed</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>SBI Holdings</t>
+          <t>Long Ridge Equity Partners</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
@@ -1424,7 +1513,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Institutional-only digital-asset trading venue paired with a separate central clearinghouse to reduce counterparty risk</t>
+          <t>AI-powered appraisal-management and valuation platform with capital-markets solutions for community banks and credit unions</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
@@ -1442,7 +1531,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Financial Info &amp; Analytics</t>
+          <t>Capital Markets Tech</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1457,19 +1546,21 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Norm Ai</t>
+          <t>EDX Markets</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Khosla Ventures</t>
+          <t>SBI Holdings</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>1200</v>
+        <v>76</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -1483,7 +1574,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>AI-native regulatory-compliance and legal-review platform deploying rules-trained agents for banks, insurers, asset managers and other regulated enterprises</t>
+          <t>Institutional-only digital-asset trading venue paired with a separate central clearinghouse to reduce counterparty risk</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
@@ -1501,65 +1592,251 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>Capital Markets Tech</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>GoCharting</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Long Ridge Equity Partners</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Web-native multi-asset order-flow charting and technical-analysis platform for retail and professional traders</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Corporate Financial Function</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Skello</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Bridgepoint</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Workforce-scheduling and HR-management platform for frontline, shift-based teams — rostering, time-tracking and payroll preparation</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Financial Info &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-26</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Norm Ai</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Khosla Ventures</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>AI-native regulatory-compliance and legal-review platform deploying rules-trained agents for banks, insurers, asset managers and other regulated enterprises</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
           <t>Real Estate &amp; Mortgage Tech</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>08-Jul-26</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Kord</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Guinness Ventures</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>8.6</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>FCA-regulated platform unifying identity/AML checks and client-money payment processing for estate agents, conveyancers and law firms</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M7"/>
+  <autoFilter ref="A3:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
